--- a/Donnees/Statistiques Démographiques et sociales/Education/Tableaux Education_portail.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Education/Tableaux Education_portail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Education\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783FB5C1-06A1-4A73-AAA8-EB77A5C09F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AC6F55-D296-4DF6-81A8-77964702B614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F576A4F-F94E-4D0F-B3FB-7D4F02E6ECAF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{1F576A4F-F94E-4D0F-B3FB-7D4F02E6ECAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -175,9 +175,6 @@
     <t>100.8</t>
   </si>
   <si>
-    <t>Source : ANSADE, RGPH 2000-2023</t>
-  </si>
-  <si>
     <t>2000~Masculin</t>
   </si>
   <si>
@@ -238,16 +235,19 @@
     <t>2023~Féminin</t>
   </si>
   <si>
-    <t>Tableau: Taux brut de scolarisation pour le fondamentale selon la wilaya et par sexe, 2000-2023</t>
-  </si>
-  <si>
-    <t>Tableau : Evolution du taux brut de scolarisation dans le fondamentale (en %) par milieu de résdence selon le sexe durant la période 2000-2023</t>
-  </si>
-  <si>
-    <t>Tableau : Evolution du taux d’analphabétisme selon la wilaya et le sexe durant la période 2000-2023</t>
-  </si>
-  <si>
     <t>2023~Ensemble</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.1 : Evolution du taux d’analphabétisme selon la wilaya et le sexe durant la période 2000-2023</t>
+  </si>
+  <si>
+    <t>Source : RGPH/2000-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.3: Evolution du taux brut de scolarisation dans le fondamentale (en %) par milieu de résdence selon le sexe durant la période 2000-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.2: Taux brut de scolarisation pour le fondamentale selon la wilaya et par sexe, 2000-2023</t>
   </si>
 </sst>
 </file>
@@ -911,7 +911,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
@@ -919,31 +919,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>53</v>
-      </c>
       <c r="H2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
@@ -1474,7 +1474,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1495,7 +1495,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -1505,18 +1505,18 @@
     <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="32"/>
       <c r="B2" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>64</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="20">
         <v>68</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="4" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>18</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="5" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="6" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>43</v>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="7" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>23</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="8" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="21" t="s">
         <v>26</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="9" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>45</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="10" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>29</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>32</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="33" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B12" s="33"/>
       <c r="C12" s="33"/>
@@ -1670,7 +1670,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="37" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -1687,31 +1687,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>52</v>
-      </c>
       <c r="G2" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="25" t="s">
-        <v>67</v>
-      </c>
       <c r="J2" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
